--- a/data/trans_orig/Q70-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q70-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,48</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,63</t>
+          <t>0,61; 3,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 6,47</t>
+          <t>0,47; 6,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,83</t>
+          <t>0,51; 2,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,3</t>
+          <t>0,38; 3,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,53</t>
+          <t>0,44; 2,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,4</t>
+          <t>0,07; 0,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,88</t>
+          <t>0,16; 0,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,91</t>
+          <t>0,97; 4,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,22</t>
+          <t>0,66; 2,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,23</t>
+          <t>0,32; 3,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,4</t>
+          <t>0,4; 1,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,93</t>
+          <t>0,74; 2,67</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,69</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,79</t>
+          <t>5,35</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>5,35</t>
         </is>
       </c>
     </row>
@@ -856,32 +856,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,07</t>
+          <t>0,6; 2,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,75</t>
+          <t>0,42; 2,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,48</t>
+          <t>0,83; 2,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 13,95</t>
+          <t>2,14; 12,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,62</t>
+          <t>0,72; 1,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,15</t>
+          <t>0,44; 1,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,27 +891,27 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 7,84</t>
+          <t>3,39; 8,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,65</t>
+          <t>0,73; 1,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,88</t>
+          <t>0,55; 1,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,17</t>
+          <t>0,92; 2,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,93</t>
+          <t>3,31; 9,36</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,6</t>
+          <t>4,94</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,26</t>
+          <t>9,73</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>6,98</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,69</t>
+          <t>0,82; 1,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,76</t>
+          <t>0,68; 1,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,96</t>
+          <t>0,87; 3,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,72; 8,94</t>
+          <t>3,26; 7,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,65</t>
+          <t>1,13; 4,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 7,64</t>
+          <t>0,63; 7,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,42</t>
+          <t>1,54; 6,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 14,76</t>
+          <t>6,75; 13,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,5</t>
+          <t>1,04; 2,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,56</t>
+          <t>0,82; 3,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,39</t>
+          <t>1,33; 3,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,28</t>
+          <t>5,31; 9,49</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>8,1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,05</t>
+          <t>7,81</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,13</t>
+          <t>0,75; 3,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,59</t>
+          <t>0,94; 4,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,93</t>
+          <t>1,39; 7,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,68; 9,46</t>
+          <t>5,53; 12,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 14,26</t>
+          <t>1,48; 13,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 8,45</t>
+          <t>0,68; 8,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,65</t>
+          <t>1,04; 9,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,52</t>
+          <t>5,59; 10,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,15</t>
+          <t>1,26; 4,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,42</t>
+          <t>1,08; 4,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,39</t>
+          <t>1,63; 5,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 8,35</t>
+          <t>6,06; 10,37</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>8,8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,68</t>
+          <t>14,75</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,01</t>
+          <t>11,27</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 11,01</t>
+          <t>1,28; 11,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 16,05</t>
+          <t>0,58; 15,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 13,43</t>
+          <t>1,02; 11,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 14,3</t>
+          <t>5,78; 13,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,91</t>
+          <t>0,44; 1,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 17,76</t>
+          <t>2,92; 18,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,28</t>
+          <t>0,5; 2,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,75; 23,17</t>
+          <t>10,13; 21,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 8,02</t>
+          <t>1,12; 7,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 11,97</t>
+          <t>2,14; 11,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 8,16</t>
+          <t>1,07; 7,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,2; 16,08</t>
+          <t>8,67; 15,19</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>2,51</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,61</t>
+          <t>7,54</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>5,02</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,93</t>
+          <t>0,57; 6,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 16,19</t>
+          <t>3,16; 16,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,49; 9,61</t>
+          <t>2,7; 10,14</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>7,68</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>7,68</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>6,33</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8,13</t>
+          <t>8,4</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>7,24</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,05</t>
+          <t>1,08; 2,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,74</t>
+          <t>1,12; 2,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,55</t>
+          <t>1,39; 3,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,79</t>
+          <t>5,07; 8,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,29</t>
+          <t>1,26; 3,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,77</t>
+          <t>1,14; 3,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,38</t>
+          <t>1,29; 3,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,23; 9,95</t>
+          <t>7,1; 10,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,15</t>
+          <t>1,23; 2,19</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,59</t>
+          <t>1,24; 2,6</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,94</t>
+          <t>1,57; 2,9</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,34</t>
+          <t>6,26; 8,64</t>
         </is>
       </c>
     </row>
